--- a/songs/ILoveIt_v1/quelle/struktur.xlsx
+++ b/songs/ILoveIt_v1/quelle/struktur.xlsx
@@ -436,15 +436,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,7 @@
       <c r="C2" s="2" t="n">
         <v>9</v>
       </c>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -478,6 +480,7 @@
       <c r="C3" s="2" t="n">
         <v>120</v>
       </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -488,6 +491,7 @@
       <c r="C4" s="2" t="n">
         <v>0.375</v>
       </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -502,20 +506,25 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Effektidee</t>
+          <t>Effekt (füllt KI)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -530,13 +539,19 @@
           <t>pause</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(5250, 5)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>progBlack(5250, 5)</t>
         </is>
@@ -551,13 +566,19 @@
           <t>synth intro</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(8000, 6, 10)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>progPalette(8000, 6, 10)</t>
         </is>
@@ -572,13 +593,19 @@
           <t>verse 1</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(16000, 15, 1000)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>progFullColors(16000, 15, 1000)</t>
         </is>
@@ -593,13 +620,19 @@
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(8000, 1000, 20, 5, 26, 5, false, 4)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(8000, 1000, 20, 5, 26, 5, false, 4)</t>
         </is>
@@ -614,13 +647,19 @@
           <t>verse 2</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progMatrixScanner(16000, 25)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(16000, 25)</t>
         </is>
@@ -635,13 +674,19 @@
           <t>chorus 2</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(8000, 1000, 30, 5, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(8000, 1000, 30, 5, 26, 5, true, 3)</t>
         </is>
@@ -656,13 +701,19 @@
           <t>youre on a different road</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(16000, 11, 35)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>progPalette(16000, 11, 35)</t>
         </is>
@@ -677,13 +728,19 @@
           <t>i love it</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(16000, 500, 40, 5, 26, 5, false, 4)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16000, 500, 40, 5, 26, 5, false, 4)</t>
         </is>
@@ -698,13 +755,19 @@
           <t>verse 3</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(16000, 45, 500)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>progFullColors(16000, 45, 500)</t>
         </is>
@@ -719,13 +782,19 @@
           <t>chorus 3</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(16000, 500, 50, 5, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16000, 500, 50, 5, 26, 5, true, 3)</t>
         </is>
@@ -740,13 +809,19 @@
           <t>youre on a different road</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(14000, 55, 50, true, false)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(14000, 55, 50, true, false)</t>
         </is>
@@ -761,13 +836,19 @@
           <t>STOP</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(2000, 60)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>progBlack(2000, 60)</t>
         </is>
@@ -782,13 +863,19 @@
           <t>chorus 4</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(16000, 500, 65, 5, 26, 5, false, 4)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16000, 500, 65, 5, 26, 5, false, 4)</t>
         </is>
@@ -803,13 +890,19 @@
           <t>chorus 5</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(8000, 6, 70)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8000, 6, 70)</t>
         </is>
@@ -829,10 +922,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>0</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/ILoveIt_v1/quelle/struktur.xlsx
+++ b/songs/ILoveIt_v1/quelle/struktur.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_DATEN\PlatformIO\Projects\LED-GIT_on_YULC\songs\ILoveIt_v1\quelle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74B9C6E-2C7F-4153-B182-6C26243E068E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5912D3-6F8F-4AD9-8F79-6B7FAF88DC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1644" yWindow="11412" windowWidth="27648" windowHeight="12276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9936" yWindow="12864" windowWidth="27648" windowHeight="12276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Struktur" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
   <si>
     <t>I Love It</t>
   </si>
@@ -138,7 +138,8 @@
   </si>
   <si>
     <t>progPalette(16000, 11, 35)
-Alter Effekt: grüner Verlauf, der zu Weiß aufhellt.</t>
+Ausgabe: Blinder bei 15500 ms, 1000 ms lang, Blinder blendet 0 ms ein, 500 ms voll, 500 ms aus
+Alter Effekt: grüner Verlauf, der zu Weiß aufhellt. Auf der letzten Viertel (Snarewirbel) ein starker Blinder, der bis zum Part-Ende voll steht.</t>
   </si>
   <si>
     <t>progPalette(16000, 11, 35)</t>
@@ -185,7 +186,8 @@
   </si>
   <si>
     <t>progBlack(2000, 60)
-Alter Effekt: 1 Takt schwarz.</t>
+Ausgabe: Blinder bei 0 ms, 500 ms lang
+Kurzer Blinder auf die Eins, der in einem Beat abklingt - danach der Rest des Takts schwarz.</t>
   </si>
   <si>
     <t>progBlack(2000, 60)</t>
@@ -195,7 +197,8 @@
   </si>
   <si>
     <t>progSternNeu(16000, 500, 65, 5, 26, 5, false, 4)
-Alter Effekt: drehender Stern, fest in der Mitte, Farbwechsel pro Beat.</t>
+Ausgabe: Blinder bei 0 ms, 1000 ms lang
+Blinder auf den Einsatz (klingt über 2 Beats ab), darunter der alte Effekt: drehender Stern, fest in der Mitte, Farbwechsel pro Beat.</t>
   </si>
   <si>
     <t>progSternNeu(16000, 500, 65, 5, 26, 5, false, 4)</t>
@@ -217,13 +220,10 @@
     <t>10 sek. BLACK</t>
   </si>
   <si>
-    <t>kurzer blinder vor der BLACK phase</t>
-  </si>
-  <si>
-    <t>blinder am anfang</t>
-  </si>
-  <si>
-    <t>am ende auf der letzten viertel starker BLINDER (auf snarewirbel)</t>
+    <t>der blinder am ende wikrt nicht! Zu wenig sichtbares reinblenden und zu kurz</t>
+  </si>
+  <si>
+    <t>Starker blinder am ende</t>
   </si>
 </sst>
 </file>
@@ -659,7 +659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>0</v>
       </c>
@@ -679,7 +679,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -699,7 +699,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -719,7 +719,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>15</v>
       </c>
@@ -739,7 +739,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>19</v>
       </c>
@@ -759,7 +759,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>27</v>
       </c>
@@ -779,7 +779,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>31</v>
       </c>
@@ -790,7 +790,7 @@
         <v>31</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5">
@@ -801,7 +801,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>39</v>
       </c>
@@ -821,7 +821,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>47</v>
       </c>
@@ -841,7 +841,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>55</v>
       </c>
@@ -861,7 +861,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>63</v>
       </c>
@@ -881,7 +881,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>70</v>
       </c>
@@ -891,9 +891,7 @@
       <c r="C17" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>55</v>
-      </c>
+      <c r="D17" s="6"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5">
         <f t="shared" si="0"/>
@@ -903,7 +901,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>71</v>
       </c>
@@ -913,9 +911,7 @@
       <c r="C18" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>56</v>
-      </c>
+      <c r="D18" s="6"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5">
         <f t="shared" si="0"/>
@@ -925,7 +921,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>79</v>
       </c>
@@ -935,7 +931,9 @@
       <c r="C19" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="6"/>
+      <c r="D19" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5">
         <f t="shared" si="0"/>

--- a/songs/ILoveIt_v1/quelle/struktur.xlsx
+++ b/songs/ILoveIt_v1/quelle/struktur.xlsx
@@ -534,7 +534,7 @@
     </row>
     <row r="6" ht="28.8" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
     </row>
     <row r="7" ht="28.8" customHeight="1">
       <c r="A7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
     </row>
     <row r="8" ht="28.8" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
     </row>
     <row r="9" ht="43.2" customHeight="1">
       <c r="A9" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
     </row>
     <row r="10" ht="28.8" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
     </row>
     <row r="11" ht="28.8" customHeight="1">
       <c r="A11" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
     </row>
     <row r="12" ht="28.8" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
     </row>
     <row r="13" ht="28.8" customHeight="1">
       <c r="A13" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
     </row>
     <row r="14" ht="28.8" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
     </row>
     <row r="15" ht="28.8" customHeight="1">
       <c r="A15" s="4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
     </row>
     <row r="16" ht="28.8" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
     </row>
     <row r="17" ht="28.8" customHeight="1">
       <c r="A17" s="4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
     </row>
     <row r="18" ht="28.8" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
     </row>
     <row r="19" ht="28.8" customHeight="1">
       <c r="A19" s="4" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>

--- a/songs/ILoveIt_v1/quelle/struktur.xlsx
+++ b/songs/ILoveIt_v1/quelle/struktur.xlsx
@@ -438,16 +438,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,6 +473,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -483,6 +485,7 @@
         <v>120</v>
       </c>
       <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -494,6 +497,7 @@
         <v>0.375</v>
       </c>
       <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -518,15 +522,20 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Neuer Vorschlag (KI)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -548,12 +557,13 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>progBlack(5250, 5)</t>
         </is>
@@ -575,12 +585,17 @@
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Szene Palette, NEON, pumpt im Beat (pulse 40) - statt weißer Wellen.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>progPalette(8000, 6, 10)</t>
         </is>
@@ -602,12 +617,17 @@
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Szene Colors, NEON, soft 30: wie bisher eine Farbe alle 2 Beats, aber feste Farben und kurze Blende.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>progFullColors(16000, 15, 1000)</t>
         </is>
@@ -629,12 +649,17 @@
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Stern bleibt (NEON, soft 30). Auf der Matrix "I LOVE IT" (ein Wort pro Beat, IT bleibt stehen) über dem Stern - nur wenn es den Titel-Lauftext nach dem Vorspann nicht stört.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(8000, 1000, 20, 5, 26, 5, false, 4)</t>
         </is>
@@ -656,12 +681,17 @@
         </is>
       </c>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Szene Call Response, NEON: Bühnenhälften blitzen abwechselnd (bisher Scanner).</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(16000, 25)</t>
         </is>
@@ -683,12 +713,17 @@
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Stern, NEON; Lampen blitzen weiß auf 2 und 4.</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(8000, 1000, 30, 5, 26, 5, true, 3)</t>
         </is>
@@ -715,12 +750,17 @@
           <t>der blinder am ende wikrt nicht! Zu wenig sichtbares reinblenden und zu kurz</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Szene DNA Flip Scroll, TOXIC (grün wie bisher): Helix auf der Matrix, alle anderen pulsieren einmal je Takt. Der Blinder im letzten Takt bleibt.</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>progPalette(16000, 11, 35)</t>
         </is>
@@ -742,12 +782,17 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Stern, SUNSET, Blinder auf den Einsatz (2 Beats).</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16000, 500, 40, 5, 26, 5, false, 4)</t>
         </is>
@@ -769,12 +814,17 @@
         </is>
       </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Szene Colors Wave, NEON, soft 60: die Farbe wandert pro Beat von Gerät zu Gerät.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>progFullColors(16000, 45, 500)</t>
         </is>
@@ -796,12 +846,17 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Stern, SUNSET, Lampen-Backbeat.</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16000, 500, 50, 5, 26, 5, true, 3)</t>
         </is>
@@ -823,12 +878,17 @@
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Wasserringe bleiben; darüber baut sich ein Glitzern auf (Ebene Sparkle, fade_in über den Part) bis zum STOP.</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(14000, 55, 50, true, false)</t>
         </is>
@@ -851,12 +911,13 @@
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>progBlack(2000, 60)</t>
         </is>
@@ -879,12 +940,17 @@
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Szene Star, FIRE - der Blinder am Anfang bleibt.</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16000, 500, 65, 5, 26, 5, false, 4)</t>
         </is>
@@ -911,12 +977,17 @@
           <t>Starker blinder am ende</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Szene Sparkle, FIRE (Einzelblitze wie bisher, in Feuerfarben); der starke Schluss-Blinder bleibt.</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8000, 6, 70)</t>
         </is>
@@ -936,10 +1007,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>0</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/ILoveIt_v1/quelle/struktur.xlsx
+++ b/songs/ILoveIt_v1/quelle/struktur.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>progBlack(5250, 5)
+          <t>progBlack(5250, 3)
 Alles schwarz bis zum Intro (die Matrix zeigt den Titel-Lauftext).</t>
         </is>
       </c>
@@ -580,7 +580,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>progPalette(8000, 6, 10)
+          <t>progPalette(8000, 6, 4)
 Alter Effekt: weiße Wellen, weich an- und abschwellend.</t>
         </is>
       </c>
@@ -612,7 +612,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>progFullColors(16000, 15, 1000)
+          <t>progFullColors(16000, 5, 1000)
 Alter Effekt: alle LEDs einfarbig, alle 2 Beats eine neue Farbe.</t>
         </is>
       </c>
@@ -644,7 +644,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>progSternNeu(8000, 1000, 20, 5, 26, 5, false, 4)
+          <t>progSternNeu(8000, 1000, 8, 5, 26, 5, false, 4)
 Alter Effekt: drehender Stern, fest in der Mitte, Farbwechsel alle 2 Beats. Hier steigt auch der Trailer (Song 80) ein.</t>
         </is>
       </c>
@@ -676,7 +676,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>progMatrixScanner(16000, 25)
+          <t>progMatrixScanner(16000, 9)
 Alter Effekt: Scanner, eine Leuchtlinie fährt hin und her.</t>
         </is>
       </c>
@@ -708,7 +708,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>progSternNeu(8000, 1000, 30, 5, 26, 5, true, 3)
+          <t>progSternNeu(8000, 1000, 10, 5, 26, 5, true, 3)
 Alter Effekt: drehender, wandernder Stern, Farbwechsel alle 2 Beats.</t>
         </is>
       </c>
@@ -740,7 +740,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>progPalette(16000, 11, 35)
+          <t>progPalette(16000, 11, 11)
 Ausgabe: Blinder voll bei 15000 ms, 2500 ms lang, Blinder blendet in den 1000 ms davor ein, 1000 ms voll, 500 ms aus
 Alter Effekt: grüner Verlauf, der zu Weiß aufhellt. Im letzten Takt (Snarewirbel) blendet ein starker Blinder zwei Beats lang ein und steht dann zwei Beats bis zum Part-Ende voll.</t>
         </is>
@@ -777,7 +777,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>progSternNeu(16000, 500, 40, 5, 26, 5, false, 4)
+          <t>progSternNeu(16000, 500, 12, 5, 26, 5, false, 4)
 Alter Effekt: drehender Stern, fest in der Mitte, Farbwechsel pro Beat.</t>
         </is>
       </c>
@@ -809,7 +809,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>progFullColors(16000, 45, 500)
+          <t>progFullColors(16000, 13, 500)
 Alter Effekt: alle LEDs einfarbig, pro Beat eine neue Farbe.</t>
         </is>
       </c>
@@ -841,7 +841,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>progSternNeu(16000, 500, 50, 5, 26, 5, true, 3)
+          <t>progSternNeu(16000, 500, 14, 5, 26, 5, true, 3)
 Alter Effekt: drehender, wandernder Stern, Farbwechsel pro Beat.</t>
         </is>
       </c>
@@ -873,7 +873,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>progWaterRipple(14000, 55, 50, true, false)
+          <t>progWaterRipple(14000, 15, 50, true, false)
 Alter Effekt: Wasserringe an zufälligen Stellen, mit Farbverlauf.</t>
         </is>
       </c>
@@ -905,7 +905,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>progBlack(2000, 60)
+          <t>progBlack(2000, 16)
 Ausgabe: Blinder bei 0 ms, 500 ms lang
 Kurzer Blinder auf die Eins, der in einem Beat abklingt - danach der Rest des Takts schwarz.</t>
         </is>
@@ -934,7 +934,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>progSternNeu(16000, 500, 65, 5, 26, 5, false, 4)
+          <t>progSternNeu(16000, 500, 17, 5, 26, 5, false, 4)
 Ausgabe: Blinder bei 0 ms, 1000 ms lang
 Blinder auf den Einsatz (klingt über 2 Beats ab), darunter der alte Effekt: drehender Stern, fest in der Mitte, Farbwechsel pro Beat.</t>
         </is>
@@ -967,7 +967,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>progFastBlingBling(8000, 6, 70)
+          <t>progFastBlingBling(8000, 6, 18)
 Ausgabe: Blinder bei 7500 ms, 1000 ms lang, Blinder blendet 0 ms ein, 500 ms voll, 500 ms aus
 Alter Effekt: schnelle Einzelblitze zum Schluss. Auf der letzten Viertel ein starker Blinder, der voll stehen bleibt und danach 5 Sekunden lang ins Schluss-Schwarz ausklingt.</t>
         </is>

--- a/songs/ILoveIt_v1/quelle/struktur.xlsx
+++ b/songs/ILoveIt_v1/quelle/struktur.xlsx
@@ -31,7 +31,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,7 +62,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -73,6 +79,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -438,17 +447,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,6 +484,7 @@
       </c>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -486,6 +497,7 @@
       </c>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -498,6 +510,7 @@
       </c>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -517,25 +530,30 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Alter Effekt (temporär)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Änderungswunsch</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Neuer Vorschlag (KI)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -558,12 +576,13 @@
       </c>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>progBlack(5250, 5)</t>
         </is>
@@ -585,17 +604,18 @@
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Szene Palette, NEON, pumpt im Beat (pulse 40) - statt weißer Wellen.</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>progPalette(8000, 6, 10)</t>
         </is>
@@ -610,24 +630,30 @@
           <t>verse 1</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE, Farben SCHEME_NEON
+Strophe neu (18.10.2026, statt der alten Vollfarben): dezent im Beat - Zonen der Gitarre, Lichtschuss in den Lampen, Plasma-Wolken in Pink/Cyan/Violett auf der Matrix</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>progFullColors(16000, 5, 1000)
 Alter Effekt: alle LEDs einfarbig, alle 2 Beats eine neue Farbe.</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Szene Colors, NEON, soft 30: wie bisher eine Farbe alle 2 Beats, aber feste Farben und kurze Blende.</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>progFullColors(16000, 15, 1000)</t>
         </is>
@@ -649,17 +675,18 @@
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Stern bleibt (NEON, soft 30). Auf der Matrix "I LOVE IT" (ein Wort pro Beat, IT bleibt stehen) über dem Stern - nur wenn es den Titel-Lauftext nach dem Vorspann nicht stört.</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(8000, 1000, 20, 5, 26, 5, false, 4)</t>
         </is>
@@ -674,24 +701,30 @@
           <t>verse 2</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_HEART, Farben SCHEME_SUNSET
+Strophe neu (18.10.2026, statt des alten Scanners): alle Geräte schlagen auf jedem Beat wie ein Herz in Orange/Pink/Lila, die Matrix zeigt eine Lissajous-Schleife</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(16000, 9)
 Alter Effekt: Scanner, eine Leuchtlinie fährt hin und her.</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Szene Call Response, NEON: Bühnenhälften blitzen abwechselnd (bisher Scanner).</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(16000, 25)</t>
         </is>
@@ -713,17 +746,18 @@
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Stern, NEON; Lampen blitzen weiß auf 2 und 4.</t>
         </is>
       </c>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(8000, 1000, 30, 5, 26, 5, true, 3)</t>
         </is>
@@ -745,22 +779,23 @@
 Alter Effekt: grüner Verlauf, der zu Weiß aufhellt. Im letzten Takt (Snarewirbel) blendet ein starker Blinder zwei Beats lang ein und steht dann zwei Beats bis zum Part-Ende voll.</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>der blinder am ende wikrt nicht! Zu wenig sichtbares reinblenden und zu kurz</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Szene DNA Flip Scroll, TOXIC (grün wie bisher): Helix auf der Matrix, alle anderen pulsieren einmal je Takt. Der Blinder im letzten Takt bleibt.</t>
         </is>
       </c>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>progPalette(16000, 11, 35)</t>
         </is>
@@ -782,17 +817,18 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Stern, SUNSET, Blinder auf den Einsatz (2 Beats).</t>
         </is>
       </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16000, 500, 40, 5, 26, 5, false, 4)</t>
         </is>
@@ -807,24 +843,30 @@
           <t>verse 3</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE, Farben SCHEME_NEON
+wie verse 1: Zonen im Beat, Lichtschuss, Plasma-Wolken auf der Matrix</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>progFullColors(16000, 13, 500)
 Alter Effekt: alle LEDs einfarbig, pro Beat eine neue Farbe.</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>Szene Colors Wave, NEON, soft 60: die Farbe wandert pro Beat von Gerät zu Gerät.</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>progFullColors(16000, 45, 500)</t>
         </is>
@@ -846,17 +888,18 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>Stern, SUNSET, Lampen-Backbeat.</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16000, 500, 50, 5, 26, 5, true, 3)</t>
         </is>
@@ -878,17 +921,18 @@
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>Wasserringe bleiben; darüber baut sich ein Glitzern auf (Ebene Sparkle, fade_in über den Part) bis zum STOP.</t>
         </is>
       </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(14000, 55, 50, true, false)</t>
         </is>
@@ -912,12 +956,13 @@
       </c>
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>progBlack(2000, 60)</t>
         </is>
@@ -940,17 +985,18 @@
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>Szene Star, FIRE - der Blinder am Anfang bleibt.</t>
         </is>
       </c>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16000, 500, 65, 5, 26, 5, false, 4)</t>
         </is>
@@ -972,22 +1018,23 @@
 Alter Effekt: schnelle Einzelblitze zum Schluss. Auf der letzten Viertel ein starker Blinder, der voll stehen bleibt und danach 5 Sekunden lang ins Schluss-Schwarz ausklingt.</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Starker blinder am ende</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Szene Sparkle, FIRE (Einzelblitze wie bisher, in Feuerfarben); der starke Schluss-Blinder bleibt.</t>
         </is>
       </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8000, 6, 70)</t>
         </is>
@@ -1007,10 +1054,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <f>$C$3</f>
         <v/>
       </c>
